--- a/tools/importer/reports/import-tatacars.report.xlsx
+++ b/tools/importer/reports/import-tatacars.report.xlsx
@@ -229,7 +229,7 @@
     <t>tata-cars-footer</t>
   </si>
   <si>
-    <t>2026-10-07T13:45:27.837Z</t>
+    <t>2026-10-08T05:50:02.838Z</t>
   </si>
   <si>
     <t>Tata Cars footer fragment: brand, newsletter (form-contact), range + links, contact + social</t>
@@ -244,7 +244,7 @@
     <t>tata-cars-nav</t>
   </si>
   <si>
-    <t>2026-10-07T13:45:23.575Z</t>
+    <t>2026-10-08T05:49:57.308Z</t>
   </si>
   <si>
     <t>Tata Cars header fragment: brand | sections | tools</t>
@@ -262,7 +262,7 @@
     <t>tata-cars</t>
   </si>
   <si>
-    <t>2026-10-07T13:45:18.050Z</t>
+    <t>2026-10-08T05:49:53.079Z</t>
   </si>
   <si>
     <t>TATA.CARS | Skip the waitlist. Secure yours today.</t>

--- a/tools/importer/reports/import-tatacars.report.xlsx
+++ b/tools/importer/reports/import-tatacars.report.xlsx
@@ -229,7 +229,7 @@
     <t>tata-cars-footer</t>
   </si>
   <si>
-    <t>2026-10-08T05:50:02.838Z</t>
+    <t>2026-10-08T06:33:05.150Z</t>
   </si>
   <si>
     <t>Tata Cars footer fragment: brand, newsletter (form-contact), range + links, contact + social</t>
@@ -244,7 +244,7 @@
     <t>tata-cars-nav</t>
   </si>
   <si>
-    <t>2026-10-08T05:49:57.308Z</t>
+    <t>2026-10-08T06:33:00.408Z</t>
   </si>
   <si>
     <t>Tata Cars header fragment: brand | sections | tools</t>
@@ -262,7 +262,7 @@
     <t>tata-cars</t>
   </si>
   <si>
-    <t>2026-10-08T05:49:53.079Z</t>
+    <t>2026-10-08T06:32:53.985Z</t>
   </si>
   <si>
     <t>TATA.CARS | Skip the waitlist. Secure yours today.</t>

--- a/tools/importer/reports/import-tatacars.report.xlsx
+++ b/tools/importer/reports/import-tatacars.report.xlsx
@@ -229,7 +229,7 @@
     <t>tata-cars-footer</t>
   </si>
   <si>
-    <t>2026-10-08T06:33:05.150Z</t>
+    <t>2026-10-08T07:11:36.308Z</t>
   </si>
   <si>
     <t>Tata Cars footer fragment: brand, newsletter (form-contact), range + links, contact + social</t>
@@ -244,7 +244,7 @@
     <t>tata-cars-nav</t>
   </si>
   <si>
-    <t>2026-10-08T06:33:00.408Z</t>
+    <t>2026-10-08T07:11:31.607Z</t>
   </si>
   <si>
     <t>Tata Cars header fragment: brand | sections | tools</t>
@@ -262,7 +262,7 @@
     <t>tata-cars</t>
   </si>
   <si>
-    <t>2026-10-08T06:32:53.985Z</t>
+    <t>2026-10-08T07:11:27.693Z</t>
   </si>
   <si>
     <t>TATA.CARS | Skip the waitlist. Secure yours today.</t>
